--- a/ig/DM-OCTOBRE-2025/ValueSet-JDV-J209-TypeSavoirFaire-ROR.xlsx
+++ b/ig/DM-OCTOBRE-2025/ValueSet-JDV-J209-TypeSavoirFaire-ROR.xlsx
@@ -102,7 +102,7 @@
     <t>C</t>
   </si>
   <si>
-    <t>Compétence</t>
+    <t>Compétence de médecine</t>
   </si>
   <si>
     <t>CAPA</t>
